--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ65"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7746,37 +7746,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>115892919</v>
+        <v>137390012</v>
       </c>
       <c r="B59" t="n">
-        <v>56837</v>
+        <v>56918</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>206002</v>
+        <v>206000</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Gråskimlig fladdermus</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Vespertilio murinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7786,29 +7786,25 @@
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>ultraljudsdetektor</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bräcke Skog 540, Boh</t>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>318085</v>
+        <v>318108</v>
       </c>
       <c r="R59" t="n">
-        <v>6444651</v>
+        <v>6444642</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7832,22 +7828,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7873,13 +7869,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115892919</t>
+          <t>https://artportalen.se/Sighting/137390012</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119929467</v>
+        <v>115892919</v>
       </c>
       <c r="B60" t="n">
         <v>56837</v>
@@ -7935,10 +7931,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>318093</v>
+        <v>318085</v>
       </c>
       <c r="R60" t="n">
-        <v>6444648</v>
+        <v>6444651</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7965,22 +7961,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8000,39 +7996,39 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emily Macgregor, Joachim Rosengren</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119929467</t>
+          <t>https://artportalen.se/Sighting/115892919</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>104140919</v>
+        <v>119929467</v>
       </c>
       <c r="B61" t="n">
-        <v>58826</v>
+        <v>56837</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>208242</v>
+        <v>206002</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8045,25 +8041,36 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+          <t>Bräcke Skog 540, Boh</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>318070</v>
+        <v>318093</v>
       </c>
       <c r="R61" t="n">
-        <v>6444646</v>
+        <v>6444648</v>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8087,12 +8094,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8112,22 +8129,22 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Emily Macgregor, Joachim Rosengren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104140919</t>
+          <t>https://artportalen.se/Sighting/119929467</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>103929451</v>
+        <v>104140919</v>
       </c>
       <c r="B62" t="n">
-        <v>58790</v>
+        <v>58826</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8135,16 +8152,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8154,17 +8171,13 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8173,13 +8186,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>318077</v>
+        <v>318070</v>
       </c>
       <c r="R62" t="n">
-        <v>6444630</v>
+        <v>6444646</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8203,22 +8216,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8244,16 +8247,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103929451</t>
+          <t>https://artportalen.se/Sighting/104140919</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>103929456</v>
+        <v>103929451</v>
       </c>
       <c r="B63" t="n">
-        <v>58817</v>
+        <v>58790</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8261,21 +8264,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8299,10 +8302,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>318086</v>
+        <v>318077</v>
       </c>
       <c r="R63" t="n">
-        <v>6444626</v>
+        <v>6444630</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8334,7 +8337,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8344,7 +8347,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8370,58 +8373,68 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103929456</t>
+          <t>https://artportalen.se/Sighting/103929451</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>116117901</v>
+        <v>103929456</v>
       </c>
       <c r="B64" t="n">
-        <v>101897</v>
+        <v>58817</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220075</v>
+        <v>208249</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Smällen, Boh</t>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>318168</v>
+        <v>318086</v>
       </c>
       <c r="R64" t="n">
-        <v>6444641</v>
+        <v>6444626</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8445,22 +8458,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8469,34 +8482,33 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulf Nilsson</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulf Nilsson</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116117901</t>
+          <t>https://artportalen.se/Sighting/103929456</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113288922</v>
+        <v>116117901</v>
       </c>
       <c r="B65" t="n">
-        <v>57876</v>
+        <v>101897</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8504,50 +8516,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6046616</v>
+        <v>220075</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Duvhök, underarten buteoides</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Astur gentilis buteoides</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Menzbier, 1882)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>318075</v>
+        <v>318168</v>
       </c>
       <c r="R65" t="n">
-        <v>6444616</v>
+        <v>6444641</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8574,27 +8574,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>utsträckt huvud, flygande, rak stjärt.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8603,22 +8598,156 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Ulf Nilsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Ulf Nilsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116117901</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>113288922</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6046616</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Duvhök, underarten buteoides</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Astur gentilis buteoides</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Menzbier, 1882)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>318075</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6444616</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>utsträckt huvud, flygande, rak stjärt.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113288922</t>
         </is>
@@ -8690,6 +8819,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -7749,7 +7749,7 @@
         <v>137390012</v>
       </c>
       <c r="B59" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
